--- a/artfynd/A 4732-2024 artfynd.xlsx
+++ b/artfynd/A 4732-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4732-2024 artfynd.xlsx
+++ b/artfynd/A 4732-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88033439</v>
+        <v>88033464</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466717.1284879084</v>
+        <v>466850</v>
       </c>
       <c r="R2" t="n">
-        <v>6322863.988998336</v>
+        <v>6323032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,12 +772,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>naturskogsartad blockig barrskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>block och marken</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,37 +795,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88033385</v>
+        <v>88033638</v>
       </c>
       <c r="B3" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -850,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466695.178948483</v>
+        <v>466871</v>
       </c>
       <c r="R3" t="n">
-        <v>6322981.111932547</v>
+        <v>6323062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +875,9 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +892,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>naturskogsartad barrskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>grov granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,37 +915,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88063842</v>
+        <v>88063851</v>
       </c>
       <c r="B4" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +950,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -985,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466883.1517977057</v>
+        <v>466912</v>
       </c>
       <c r="R4" t="n">
-        <v>6323042.156239983</v>
+        <v>6323067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,19 +995,9 @@
           <t>2020-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +1012,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>brant i naturskogsartad barrskog</t>
+          <t>naturskogsartad barrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>grov granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,54 +1028,49 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sonja Darell</t>
+          <t>Per Darell, Sonja Darell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88063869</v>
+        <v>88063879</v>
       </c>
       <c r="B5" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1115,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466906.1926627959</v>
+        <v>466891</v>
       </c>
       <c r="R5" t="n">
-        <v>6323061.009286225</v>
+        <v>6323069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,19 +1115,9 @@
           <t>2020-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,7 +1137,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granbas</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,15 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88097787</v>
+        <v>88063917</v>
       </c>
       <c r="B6" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,26 +1166,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med honorgan</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1242,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466875.9366957326</v>
+        <v>466876</v>
       </c>
       <c r="R6" t="n">
-        <v>6323025.896264013</v>
+        <v>6323026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,19 +1239,9 @@
           <t>2020-09-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,62 +1272,56 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Sonja Darell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88175100</v>
+        <v>89318446</v>
       </c>
       <c r="B7" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bokehult, Sm</t>
+          <t>Naturskog, Kulla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466867.8404092785</v>
+        <v>466773</v>
       </c>
       <c r="R7" t="n">
-        <v>6323035.751625098</v>
+        <v>6322997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,22 +1348,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,40 +1366,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>naturskogsartad ba</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>rrskoggranhögstubbe</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Johan Marand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Johan Marand, Per Darell, Johan Blomby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89318544</v>
+        <v>89318481</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466794.2910006648</v>
+        <v>466768</v>
       </c>
       <c r="R8" t="n">
-        <v>6322971.069412604</v>
+        <v>6322993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,19 +1453,9 @@
           <t>2020-11-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-11-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,12 +1486,7 @@
         <v>89318516</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466763.7590165267</v>
+        <v>466764</v>
       </c>
       <c r="R9" t="n">
-        <v>6322969.682488543</v>
+        <v>6322970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,19 +1555,9 @@
           <t>2020-11-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-11-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,15 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88063917</v>
+        <v>89318544</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,33 +1613,21 @@
           <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med honorgan</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bokehult, Sm</t>
+          <t>Naturskog, Kulla, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466875.9366957326</v>
+        <v>466794</v>
       </c>
       <c r="R10" t="n">
-        <v>6323025.896264013</v>
+        <v>6322971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1773,22 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,28 +1672,1475 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>naturskogsartad barrskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Johan Marand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Marand, Per Darell, Johan Blomby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123236979</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullaskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466750</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6322980</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sonja Darell, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88097787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466876</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6323026</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>naturskogsartad barrskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Per Darell</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>88063842</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97733</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466883</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6323042</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>brant i naturskogsartad barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88033439</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466717</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6322864</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>block och marken</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Per Darell, Sonja Darell</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>88033569</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>466865</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6323060</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Täckte stora delar av marken</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>barrskog vid brant</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>block och marken</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Darell, Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>88033646</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>466871</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6323062</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>naturskogsartad barrskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Darell, Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>88063780</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>466873</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6323040</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>88063869</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466906</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6323061</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>naturskogsartad barrskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>granbas</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Darell, Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>98608665</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Alvesta, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>466782</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6323011</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-02-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-02-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>98609048</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Alvesta, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>466925</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6323054</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-02-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-02-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89324042</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kullaskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>466834</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6323035</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack och födosök i barrträd</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sonja Darell, Per Fogelström, Tomas Lundqvist, Uno Pettersson, Annchristin Nyström, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88175100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>466868</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6323036</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>naturskogsartad ba</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>rrskoggranhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88033385</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bokehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>466695</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6322981</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Darell, Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4732-2024 artfynd.xlsx
+++ b/artfynd/A 4732-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063851</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063879</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89318446</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89318481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89318516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89318544</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236979</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,6 +1953,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88097787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2133,6 +2198,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033439</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2258,6 +2328,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033569</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2378,6 +2453,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033646</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2493,6 +2573,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063780</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88063869</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2711,6 +2801,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98608665</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98609048</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2920,6 +3020,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89324042</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3033,6 +3138,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88175100</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3141,8 +3251,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88033385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>